--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-27T05:16:33.545Z</t>
+    <t>2026-06-28T05:05:02.899Z</t>
   </si>
   <si>
     <t>MOOG Parts | Steering, Suspension &amp; Drivetrain Parts</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-28T05:05:02.899Z</t>
+    <t>2026-06-28T05:20:15.508Z</t>
   </si>
   <si>
     <t>MOOG Parts | Steering, Suspension &amp; Drivetrain Parts</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-28T05:20:15.508Z</t>
+    <t>2026-06-28T06:47:46.551Z</t>
   </si>
   <si>
     <t>MOOG Parts | Steering, Suspension &amp; Drivetrain Parts</t>
